--- a/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/dashboard_inventory.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/07_data_analytics_reporting/dashboard_inventory.xlsx
@@ -490,15 +490,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>379</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -515,15 +515,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>836</v>
+        <v>306</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -540,11 +540,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>506</v>
+        <v>898</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -565,15 +565,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>889</v>
+        <v>254</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -590,11 +590,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>186</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -615,15 +615,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -644,11 +644,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>154</v>
+        <v>528</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -665,15 +665,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>265</v>
+        <v>443</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -694,11 +694,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>429</v>
+        <v>773</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>676</v>
+        <v>426</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -794,11 +794,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>142</v>
+        <v>845</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -840,15 +840,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>87</v>
+        <v>292</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -865,15 +865,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>475</v>
+        <v>161</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -894,11 +894,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>793</v>
+        <v>859</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -915,15 +915,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>266</v>
+        <v>656</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -940,15 +940,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>318</v>
+        <v>811</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -965,11 +965,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>497</v>
+        <v>546</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -990,15 +990,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>754</v>
+        <v>649</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -1015,11 +1015,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>273</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1040,11 +1040,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1065,15 +1065,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>892</v>
+        <v>56</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>753</v>
+        <v>344</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1115,15 +1115,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>443</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1144,11 +1144,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>666</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1165,15 +1165,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>351</v>
+        <v>422</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -1194,11 +1194,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>729</v>
+        <v>605</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1219,11 +1219,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1240,11 +1240,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>645</v>
+        <v>431</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1265,15 +1265,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>884</v>
+        <v>244</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1290,15 +1290,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>725</v>
+        <v>89</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>256</v>
+        <v>123</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1340,15 +1340,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>106</v>
+        <v>366</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>134</v>
+        <v>266</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1394,11 +1394,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>700</v>
+        <v>614</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -1415,15 +1415,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>715</v>
+        <v>648</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1440,15 +1440,15 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>719</v>
+        <v>813</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1490,15 +1490,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>90</v>
+        <v>298</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1515,11 +1515,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>427</v>
+        <v>196</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1540,15 +1540,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>176</v>
+        <v>764</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -1569,11 +1569,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>518</v>
+        <v>91</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1590,11 +1590,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>752</v>
+        <v>539</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1615,11 +1615,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>70</v>
+        <v>496</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1640,15 +1640,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>553</v>
+        <v>741</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>153</v>
+        <v>563</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>173</v>
+        <v>30</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -1715,11 +1715,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>533</v>
+        <v>398</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>26</v>
+        <v>437</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1765,15 +1765,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>725</v>
+        <v>677</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1794,11 +1794,11 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>752</v>
+        <v>465</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1815,11 +1815,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>344</v>
+        <v>38</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>736</v>
+        <v>385</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1865,15 +1865,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>87</v>
+        <v>580</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1894,11 +1894,11 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1915,15 +1915,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>411</v>
+        <v>244</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1940,15 +1940,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>396</v>
+        <v>316</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1965,15 +1965,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -1994,11 +1994,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>327</v>
+        <v>263</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>557</v>
+        <v>47</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2040,15 +2040,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>756</v>
+        <v>16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -2065,15 +2065,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>609</v>
+        <v>257</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -2094,11 +2094,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>371</v>
+        <v>727</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -2119,11 +2119,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>711</v>
+        <v>212</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2169,11 +2169,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>645</v>
+        <v>440</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>322</v>
+        <v>36</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2215,15 +2215,15 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>261</v>
+        <v>701</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -2244,11 +2244,11 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -2265,15 +2265,15 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>537</v>
+        <v>572</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -2290,15 +2290,15 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>160</v>
+        <v>593</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -2315,15 +2315,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>708</v>
+        <v>590</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>646</v>
+        <v>895</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2369,11 +2369,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -2394,11 +2394,11 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>391</v>
+        <v>640</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -2415,15 +2415,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>112</v>
+        <v>318</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Duplicate</t>
         </is>
       </c>
     </row>
@@ -2444,11 +2444,11 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>103</v>
+        <v>468</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Duplicate</t>
+          <t>Stale</t>
         </is>
       </c>
     </row>
@@ -2465,11 +2465,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>725</v>
+        <v>647</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
